--- a/results/DepMap/depmap_glioma_recurrence_scores.xlsx
+++ b/results/DepMap/depmap_glioma_recurrence_scores.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
   <si>
     <t>ModelID</t>
   </si>
@@ -91,78 +91,78 @@
     <t>T98G</t>
   </si>
   <si>
+    <t>GOS-3</t>
+  </si>
+  <si>
+    <t>U-118 MG</t>
+  </si>
+  <si>
+    <t>SNU-626</t>
+  </si>
+  <si>
+    <t>SW 1088</t>
+  </si>
+  <si>
+    <t>LN-215</t>
+  </si>
+  <si>
+    <t>Onda 8</t>
+  </si>
+  <si>
+    <t>SNU-489</t>
+  </si>
+  <si>
+    <t>SF539</t>
+  </si>
+  <si>
+    <t>LN382</t>
+  </si>
+  <si>
+    <t>SNU-738</t>
+  </si>
+  <si>
+    <t>KNS-81</t>
+  </si>
+  <si>
+    <t>SF268</t>
+  </si>
+  <si>
+    <t>LN-428</t>
+  </si>
+  <si>
+    <t>H4</t>
+  </si>
+  <si>
+    <t>GI-1</t>
+  </si>
+  <si>
+    <t>SNU-201</t>
+  </si>
+  <si>
+    <t>SF126</t>
+  </si>
+  <si>
+    <t>SNB75</t>
+  </si>
+  <si>
+    <t>no.10</t>
+  </si>
+  <si>
+    <t>TB096</t>
+  </si>
+  <si>
+    <t>U-251 MG</t>
+  </si>
+  <si>
+    <t>no.11</t>
+  </si>
+  <si>
+    <t>TM-31</t>
+  </si>
+  <si>
     <t>U-251 MG DM</t>
   </si>
   <si>
-    <t>GOS-3</t>
-  </si>
-  <si>
-    <t>U-118 MG</t>
-  </si>
-  <si>
-    <t>SNU-626</t>
-  </si>
-  <si>
-    <t>SW 1088</t>
-  </si>
-  <si>
-    <t>LN-215</t>
-  </si>
-  <si>
-    <t>Onda 8</t>
-  </si>
-  <si>
-    <t>SNU-489</t>
-  </si>
-  <si>
-    <t>SF539</t>
-  </si>
-  <si>
-    <t>LN382</t>
-  </si>
-  <si>
-    <t>SNU-738</t>
-  </si>
-  <si>
-    <t>KNS-81</t>
-  </si>
-  <si>
-    <t>SF268</t>
-  </si>
-  <si>
-    <t>LN-428</t>
-  </si>
-  <si>
-    <t>H4</t>
-  </si>
-  <si>
-    <t>GI-1</t>
-  </si>
-  <si>
-    <t>SNU-201</t>
-  </si>
-  <si>
-    <t>SF126</t>
-  </si>
-  <si>
-    <t>SNB75</t>
-  </si>
-  <si>
-    <t>no.10</t>
-  </si>
-  <si>
-    <t>TB096</t>
-  </si>
-  <si>
-    <t>U-251 MG</t>
-  </si>
-  <si>
-    <t>no.11</t>
-  </si>
-  <si>
-    <t>TM-31</t>
-  </si>
-  <si>
     <t>LN-319</t>
   </si>
   <si>
@@ -313,76 +313,76 @@
     <t>ACH-000571</t>
   </si>
   <si>
+    <t>ACH-000027</t>
+  </si>
+  <si>
+    <t>ACH-000040</t>
+  </si>
+  <si>
+    <t>ACH-000370</t>
+  </si>
+  <si>
+    <t>ACH-000437</t>
+  </si>
+  <si>
+    <t>ACH-000328</t>
+  </si>
+  <si>
+    <t>ACH-001623</t>
+  </si>
+  <si>
+    <t>ACH-000543</t>
+  </si>
+  <si>
+    <t>ACH-000273</t>
+  </si>
+  <si>
+    <t>ACH-000215</t>
+  </si>
+  <si>
+    <t>ACH-000807</t>
+  </si>
+  <si>
+    <t>ACH-000479</t>
+  </si>
+  <si>
+    <t>ACH-000655</t>
+  </si>
+  <si>
+    <t>ACH-000455</t>
+  </si>
+  <si>
+    <t>ACH-000389</t>
+  </si>
+  <si>
+    <t>ACH-000756</t>
+  </si>
+  <si>
+    <t>ACH-000623</t>
+  </si>
+  <si>
+    <t>ACH-000609</t>
+  </si>
+  <si>
+    <t>ACH-000504</t>
+  </si>
+  <si>
+    <t>ACH-001605</t>
+  </si>
+  <si>
+    <t>ACH-002806</t>
+  </si>
+  <si>
+    <t>ACH-000232</t>
+  </si>
+  <si>
+    <t>ACH-001606</t>
+  </si>
+  <si>
+    <t>ACH-000592</t>
+  </si>
+  <si>
     <t>ACH-001172</t>
-  </si>
-  <si>
-    <t>ACH-000027</t>
-  </si>
-  <si>
-    <t>ACH-000040</t>
-  </si>
-  <si>
-    <t>ACH-000370</t>
-  </si>
-  <si>
-    <t>ACH-000437</t>
-  </si>
-  <si>
-    <t>ACH-000328</t>
-  </si>
-  <si>
-    <t>ACH-001623</t>
-  </si>
-  <si>
-    <t>ACH-000543</t>
-  </si>
-  <si>
-    <t>ACH-000273</t>
-  </si>
-  <si>
-    <t>ACH-000215</t>
-  </si>
-  <si>
-    <t>ACH-000807</t>
-  </si>
-  <si>
-    <t>ACH-000479</t>
-  </si>
-  <si>
-    <t>ACH-000655</t>
-  </si>
-  <si>
-    <t>ACH-000455</t>
-  </si>
-  <si>
-    <t>ACH-000389</t>
-  </si>
-  <si>
-    <t>ACH-000756</t>
-  </si>
-  <si>
-    <t>ACH-000623</t>
-  </si>
-  <si>
-    <t>ACH-000609</t>
-  </si>
-  <si>
-    <t>ACH-000504</t>
-  </si>
-  <si>
-    <t>ACH-001605</t>
-  </si>
-  <si>
-    <t>ACH-002806</t>
-  </si>
-  <si>
-    <t>ACH-000232</t>
-  </si>
-  <si>
-    <t>ACH-001606</t>
-  </si>
-  <si>
-    <t>ACH-000592</t>
   </si>
   <si>
     <t>ACH-000128</t>
@@ -810,7 +810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1264,13 +1264,13 @@
         <v>93</v>
       </c>
       <c r="E20">
-        <v>0.2668878454540778</v>
+        <v>0.2573707892139213</v>
       </c>
       <c r="F20">
-        <v>0.4376634218735889</v>
+        <v>0.4359980032042597</v>
       </c>
       <c r="G20">
-        <v>-0.1707755764195111</v>
+        <v>-0.1786272139903385</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1287,13 +1287,13 @@
         <v>93</v>
       </c>
       <c r="E21">
-        <v>0.2573707892139213</v>
+        <v>0.2453684312798569</v>
       </c>
       <c r="F21">
-        <v>0.4359980032042597</v>
+        <v>0.454800807536055</v>
       </c>
       <c r="G21">
-        <v>-0.1786272139903385</v>
+        <v>-0.2094323762561981</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1310,13 +1310,13 @@
         <v>93</v>
       </c>
       <c r="E22">
-        <v>0.2453684312798569</v>
+        <v>0.2431509281916001</v>
       </c>
       <c r="F22">
-        <v>0.454800807536055</v>
+        <v>0.4728000580265428</v>
       </c>
       <c r="G22">
-        <v>-0.2094323762561981</v>
+        <v>-0.2296491298349427</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1333,13 +1333,13 @@
         <v>93</v>
       </c>
       <c r="E23">
-        <v>0.2431509281916001</v>
+        <v>0.2601457297961056</v>
       </c>
       <c r="F23">
-        <v>0.4728000580265428</v>
+        <v>0.4492527304830639</v>
       </c>
       <c r="G23">
-        <v>-0.2296491298349427</v>
+        <v>-0.1891070006869582</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1356,13 +1356,13 @@
         <v>93</v>
       </c>
       <c r="E24">
-        <v>0.2601457297961056</v>
+        <v>0.2503706724602608</v>
       </c>
       <c r="F24">
-        <v>0.4492527304830639</v>
+        <v>0.4600555518814893</v>
       </c>
       <c r="G24">
-        <v>-0.1891070006869582</v>
+        <v>-0.2096848794212284</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1379,13 +1379,13 @@
         <v>93</v>
       </c>
       <c r="E25">
-        <v>0.2503706724602608</v>
+        <v>0.2832876524431315</v>
       </c>
       <c r="F25">
-        <v>0.4600555518814893</v>
+        <v>0.4779733803234554</v>
       </c>
       <c r="G25">
-        <v>-0.2096848794212284</v>
+        <v>-0.1946857278803238</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1402,13 +1402,13 @@
         <v>93</v>
       </c>
       <c r="E26">
-        <v>0.2832876524431315</v>
+        <v>0.2679159716558037</v>
       </c>
       <c r="F26">
-        <v>0.4779733803234554</v>
+        <v>0.3953822676289401</v>
       </c>
       <c r="G26">
-        <v>-0.1946857278803238</v>
+        <v>-0.1274662959731365</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1425,13 +1425,13 @@
         <v>93</v>
       </c>
       <c r="E27">
-        <v>0.2679159716558037</v>
+        <v>0.2464275829297984</v>
       </c>
       <c r="F27">
-        <v>0.3953822676289401</v>
+        <v>0.439163507562295</v>
       </c>
       <c r="G27">
-        <v>-0.1274662959731365</v>
+        <v>-0.1927359246324966</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1448,13 +1448,13 @@
         <v>93</v>
       </c>
       <c r="E28">
-        <v>0.2464275829297984</v>
+        <v>0.2401267634497359</v>
       </c>
       <c r="F28">
-        <v>0.439163507562295</v>
+        <v>0.4732583681599257</v>
       </c>
       <c r="G28">
-        <v>-0.1927359246324966</v>
+        <v>-0.2331316047101898</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1471,13 +1471,13 @@
         <v>93</v>
       </c>
       <c r="E29">
-        <v>0.2401267634497359</v>
+        <v>0.2709670795500657</v>
       </c>
       <c r="F29">
-        <v>0.4732583681599257</v>
+        <v>0.4303226375339289</v>
       </c>
       <c r="G29">
-        <v>-0.2331316047101898</v>
+        <v>-0.1593555579838632</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1494,13 +1494,13 @@
         <v>93</v>
       </c>
       <c r="E30">
-        <v>0.2709670795500657</v>
+        <v>0.2418245902803803</v>
       </c>
       <c r="F30">
-        <v>0.4303226375339289</v>
+        <v>0.4957912978674535</v>
       </c>
       <c r="G30">
-        <v>-0.1593555579838632</v>
+        <v>-0.2539667075870732</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1517,13 +1517,13 @@
         <v>93</v>
       </c>
       <c r="E31">
-        <v>0.2418245902803803</v>
+        <v>0.261851108874013</v>
       </c>
       <c r="F31">
-        <v>0.4957912978674535</v>
+        <v>0.4399215503895815</v>
       </c>
       <c r="G31">
-        <v>-0.2539667075870732</v>
+        <v>-0.1780704415155684</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1540,13 +1540,13 @@
         <v>93</v>
       </c>
       <c r="E32">
-        <v>0.261851108874013</v>
+        <v>0.2375926783208048</v>
       </c>
       <c r="F32">
-        <v>0.4399215503895815</v>
+        <v>0.4550934291340179</v>
       </c>
       <c r="G32">
-        <v>-0.1780704415155684</v>
+        <v>-0.2175007508132131</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1563,13 +1563,13 @@
         <v>93</v>
       </c>
       <c r="E33">
-        <v>0.2375926783208048</v>
+        <v>0.2710681163715575</v>
       </c>
       <c r="F33">
-        <v>0.4550934291340179</v>
+        <v>0.4639641657653352</v>
       </c>
       <c r="G33">
-        <v>-0.2175007508132131</v>
+        <v>-0.1928960493937777</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1586,13 +1586,13 @@
         <v>93</v>
       </c>
       <c r="E34">
-        <v>0.2710681163715575</v>
+        <v>0.2380717357350296</v>
       </c>
       <c r="F34">
-        <v>0.4639641657653352</v>
+        <v>0.4548864962421413</v>
       </c>
       <c r="G34">
-        <v>-0.1928960493937777</v>
+        <v>-0.2168147605071117</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1609,13 +1609,13 @@
         <v>93</v>
       </c>
       <c r="E35">
-        <v>0.2380717357350296</v>
+        <v>0.2565641275603139</v>
       </c>
       <c r="F35">
-        <v>0.4548864962421413</v>
+        <v>0.4754820078606053</v>
       </c>
       <c r="G35">
-        <v>-0.2168147605071117</v>
+        <v>-0.2189178803002914</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1632,13 +1632,13 @@
         <v>93</v>
       </c>
       <c r="E36">
-        <v>0.2565641275603139</v>
+        <v>0.2320550440438896</v>
       </c>
       <c r="F36">
-        <v>0.4754820078606053</v>
+        <v>0.4581899558614276</v>
       </c>
       <c r="G36">
-        <v>-0.2189178803002914</v>
+        <v>-0.226134911817538</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1655,13 +1655,13 @@
         <v>93</v>
       </c>
       <c r="E37">
-        <v>0.2320550440438896</v>
+        <v>0.3026401839972371</v>
       </c>
       <c r="F37">
-        <v>0.4581899558614276</v>
+        <v>0.4846450105350887</v>
       </c>
       <c r="G37">
-        <v>-0.226134911817538</v>
+        <v>-0.1820048265378515</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1678,13 +1678,13 @@
         <v>93</v>
       </c>
       <c r="E38">
-        <v>0.3026401839972371</v>
+        <v>0.2494707303472156</v>
       </c>
       <c r="F38">
-        <v>0.4846450105350887</v>
+        <v>0.4340154296559723</v>
       </c>
       <c r="G38">
-        <v>-0.1820048265378515</v>
+        <v>-0.1845446993087567</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1701,13 +1701,13 @@
         <v>93</v>
       </c>
       <c r="E39">
-        <v>0.2494707303472156</v>
+        <v>0.2942363698266086</v>
       </c>
       <c r="F39">
-        <v>0.4340154296559723</v>
+        <v>0.4331407648552573</v>
       </c>
       <c r="G39">
-        <v>-0.1845446993087567</v>
+        <v>-0.1389043950286487</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1724,21 +1724,21 @@
         <v>93</v>
       </c>
       <c r="E40">
-        <v>0.2942363698266086</v>
+        <v>0.238363619886006</v>
       </c>
       <c r="F40">
-        <v>0.4331407648552573</v>
+        <v>0.4448246510407446</v>
       </c>
       <c r="G40">
-        <v>-0.1389043950286487</v>
+        <v>-0.2064610311547386</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="C41">
         <v>162</v>
@@ -1747,21 +1747,21 @@
         <v>93</v>
       </c>
       <c r="E41">
-        <v>0.2488920649150352</v>
+        <v>0.2221899720852612</v>
       </c>
       <c r="F41">
-        <v>0.4533448106421816</v>
+        <v>0.4219379443101632</v>
       </c>
       <c r="G41">
-        <v>-0.2044527457271464</v>
+        <v>-0.199747972224902</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C42">
         <v>162</v>
@@ -1770,21 +1770,21 @@
         <v>93</v>
       </c>
       <c r="E42">
-        <v>0.238363619886006</v>
+        <v>0.2779120853101851</v>
       </c>
       <c r="F42">
-        <v>0.4448246510407446</v>
+        <v>0.4725074364285801</v>
       </c>
       <c r="G42">
-        <v>-0.2064610311547386</v>
+        <v>-0.194595351118395</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C43">
         <v>162</v>
@@ -1793,21 +1793,21 @@
         <v>93</v>
       </c>
       <c r="E43">
-        <v>0.2221899720852612</v>
+        <v>0.2564132867298443</v>
       </c>
       <c r="F43">
-        <v>0.4219379443101632</v>
+        <v>0.4210732350437652</v>
       </c>
       <c r="G43">
-        <v>-0.199747972224902</v>
+        <v>-0.1646599483139209</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C44">
         <v>162</v>
@@ -1816,21 +1816,21 @@
         <v>93</v>
       </c>
       <c r="E44">
-        <v>0.2779120853101851</v>
+        <v>0.2415990434364439</v>
       </c>
       <c r="F44">
-        <v>0.4725074364285801</v>
+        <v>0.4918880173055632</v>
       </c>
       <c r="G44">
-        <v>-0.194595351118395</v>
+        <v>-0.2502889738691192</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="C45">
         <v>162</v>
@@ -1839,21 +1839,21 @@
         <v>93</v>
       </c>
       <c r="E45">
-        <v>0.2564132867298443</v>
+        <v>0.2606253995547032</v>
       </c>
       <c r="F45">
-        <v>0.4210732350437652</v>
+        <v>0.435952847745036</v>
       </c>
       <c r="G45">
-        <v>-0.1646599483139209</v>
+        <v>-0.1753274481903328</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C46">
         <v>162</v>
@@ -1862,21 +1862,21 @@
         <v>93</v>
       </c>
       <c r="E46">
-        <v>0.2415990434364439</v>
+        <v>0.2550822541784339</v>
       </c>
       <c r="F46">
-        <v>0.4918880173055632</v>
+        <v>0.4334476086451015</v>
       </c>
       <c r="G46">
-        <v>-0.2502889738691192</v>
+        <v>-0.1783653544666676</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C47">
         <v>162</v>
@@ -1885,21 +1885,21 @@
         <v>93</v>
       </c>
       <c r="E47">
-        <v>0.2606253995547032</v>
+        <v>0.2437391870189525</v>
       </c>
       <c r="F47">
-        <v>0.435952847745036</v>
+        <v>0.4855918529596026</v>
       </c>
       <c r="G47">
-        <v>-0.1753274481903328</v>
+        <v>-0.2418526659406501</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C48">
         <v>162</v>
@@ -1908,21 +1908,21 @@
         <v>93</v>
       </c>
       <c r="E48">
-        <v>0.2550822541784339</v>
+        <v>0.2865347105366505</v>
       </c>
       <c r="F48">
-        <v>0.4334476086451015</v>
+        <v>0.4286497522138619</v>
       </c>
       <c r="G48">
-        <v>-0.1783653544666676</v>
+        <v>-0.1421150416772115</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C49">
         <v>162</v>
@@ -1931,21 +1931,21 @@
         <v>93</v>
       </c>
       <c r="E49">
-        <v>0.2437391870189525</v>
+        <v>0.2426579909715945</v>
       </c>
       <c r="F49">
-        <v>0.4855918529596026</v>
+        <v>0.4545775191235149</v>
       </c>
       <c r="G49">
-        <v>-0.2418526659406501</v>
+        <v>-0.2119195281519203</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C50">
         <v>162</v>
@@ -1954,21 +1954,21 @@
         <v>93</v>
       </c>
       <c r="E50">
-        <v>0.2865347105366505</v>
+        <v>0.241564752151574</v>
       </c>
       <c r="F50">
-        <v>0.4286497522138619</v>
+        <v>0.4598727967158114</v>
       </c>
       <c r="G50">
-        <v>-0.1421150416772115</v>
+        <v>-0.2183080445642374</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C51">
         <v>162</v>
@@ -1977,21 +1977,21 @@
         <v>93</v>
       </c>
       <c r="E51">
-        <v>0.2426579909715945</v>
+        <v>0.2454051719422176</v>
       </c>
       <c r="F51">
-        <v>0.4545775191235149</v>
+        <v>0.4595812417822397</v>
       </c>
       <c r="G51">
-        <v>-0.2119195281519203</v>
+        <v>-0.2141760698400222</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C52">
         <v>162</v>
@@ -2000,21 +2000,21 @@
         <v>93</v>
       </c>
       <c r="E52">
-        <v>0.241564752151574</v>
+        <v>0.2484797530374322</v>
       </c>
       <c r="F52">
-        <v>0.4598727967158114</v>
+        <v>0.4389224414099027</v>
       </c>
       <c r="G52">
-        <v>-0.2183080445642374</v>
+        <v>-0.1904426883724705</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C53">
         <v>162</v>
@@ -2023,21 +2023,21 @@
         <v>93</v>
       </c>
       <c r="E53">
-        <v>0.2454051719422176</v>
+        <v>0.2615459572616286</v>
       </c>
       <c r="F53">
-        <v>0.4595812417822397</v>
+        <v>0.4278113540024449</v>
       </c>
       <c r="G53">
-        <v>-0.2141760698400222</v>
+        <v>-0.1662653967408163</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C54">
         <v>162</v>
@@ -2046,21 +2046,21 @@
         <v>93</v>
       </c>
       <c r="E54">
-        <v>0.2484797530374322</v>
+        <v>0.2586471190013724</v>
       </c>
       <c r="F54">
-        <v>0.4389224414099027</v>
+        <v>0.4265594455620716</v>
       </c>
       <c r="G54">
-        <v>-0.1904426883724705</v>
+        <v>-0.1679123265606992</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C55">
         <v>162</v>
@@ -2069,21 +2069,21 @@
         <v>93</v>
       </c>
       <c r="E55">
-        <v>0.2615459572616286</v>
+        <v>0.2310934592639947</v>
       </c>
       <c r="F55">
-        <v>0.4278113540024449</v>
+        <v>0.4848842989134957</v>
       </c>
       <c r="G55">
-        <v>-0.1662653967408163</v>
+        <v>-0.253790839649501</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C56">
         <v>162</v>
@@ -2092,21 +2092,21 @@
         <v>93</v>
       </c>
       <c r="E56">
-        <v>0.2586471190013724</v>
+        <v>0.3042067650173375</v>
       </c>
       <c r="F56">
-        <v>0.4265594455620716</v>
+        <v>0.445612204916185</v>
       </c>
       <c r="G56">
-        <v>-0.1679123265606992</v>
+        <v>-0.1414054398988475</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C57">
         <v>162</v>
@@ -2115,21 +2115,21 @@
         <v>93</v>
       </c>
       <c r="E57">
-        <v>0.2310934592639947</v>
+        <v>0.2408003422596814</v>
       </c>
       <c r="F57">
-        <v>0.4848842989134957</v>
+        <v>0.4909102416137068</v>
       </c>
       <c r="G57">
-        <v>-0.253790839649501</v>
+        <v>-0.2501098993540255</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C58">
         <v>162</v>
@@ -2138,21 +2138,21 @@
         <v>93</v>
       </c>
       <c r="E58">
-        <v>0.3042067650173375</v>
+        <v>0.2345321811461617</v>
       </c>
       <c r="F58">
-        <v>0.445612204916185</v>
+        <v>0.4427403888205038</v>
       </c>
       <c r="G58">
-        <v>-0.1414054398988475</v>
+        <v>-0.2082082076743421</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C59">
         <v>162</v>
@@ -2161,21 +2161,21 @@
         <v>93</v>
       </c>
       <c r="E59">
-        <v>0.2408003422596814</v>
+        <v>0.2440610760441901</v>
       </c>
       <c r="F59">
-        <v>0.4909102416137068</v>
+        <v>0.4258796247901337</v>
       </c>
       <c r="G59">
-        <v>-0.2501098993540255</v>
+        <v>-0.1818185487459437</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C60">
         <v>162</v>
@@ -2184,21 +2184,21 @@
         <v>93</v>
       </c>
       <c r="E60">
-        <v>0.2345321811461617</v>
+        <v>0.2461256971540683</v>
       </c>
       <c r="F60">
-        <v>0.4427403888205038</v>
+        <v>0.4726624583200889</v>
       </c>
       <c r="G60">
-        <v>-0.2082082076743421</v>
+        <v>-0.2265367611660206</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C61">
         <v>162</v>
@@ -2207,21 +2207,21 @@
         <v>93</v>
       </c>
       <c r="E61">
-        <v>0.2440610760441901</v>
+        <v>0.2514498273597098</v>
       </c>
       <c r="F61">
-        <v>0.4258796247901337</v>
+        <v>0.4741884995089788</v>
       </c>
       <c r="G61">
-        <v>-0.1818185487459437</v>
+        <v>-0.222738672149269</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C62">
         <v>162</v>
@@ -2230,21 +2230,21 @@
         <v>93</v>
       </c>
       <c r="E62">
-        <v>0.2461256971540683</v>
+        <v>0.2522713893930524</v>
       </c>
       <c r="F62">
-        <v>0.4726624583200889</v>
+        <v>0.4521177910376012</v>
       </c>
       <c r="G62">
-        <v>-0.2265367611660206</v>
+        <v>-0.1998464016445489</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C63">
         <v>162</v>
@@ -2253,21 +2253,21 @@
         <v>93</v>
       </c>
       <c r="E63">
-        <v>0.2514498273597098</v>
+        <v>0.2505366177852565</v>
       </c>
       <c r="F63">
-        <v>0.4741884995089788</v>
+        <v>0.4763950725794007</v>
       </c>
       <c r="G63">
-        <v>-0.222738672149269</v>
+        <v>-0.2258584547941442</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C64">
         <v>162</v>
@@ -2276,21 +2276,21 @@
         <v>93</v>
       </c>
       <c r="E64">
-        <v>0.2522713893930524</v>
+        <v>0.2690416647275762</v>
       </c>
       <c r="F64">
-        <v>0.4521177910376012</v>
+        <v>0.4937415244625256</v>
       </c>
       <c r="G64">
-        <v>-0.1998464016445489</v>
+        <v>-0.2246998597349494</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C65">
         <v>162</v>
@@ -2299,21 +2299,21 @@
         <v>93</v>
       </c>
       <c r="E65">
-        <v>0.2505366177852565</v>
+        <v>0.2487246907865033</v>
       </c>
       <c r="F65">
-        <v>0.4763950725794007</v>
+        <v>0.4577828456188182</v>
       </c>
       <c r="G65">
-        <v>-0.2258584547941442</v>
+        <v>-0.2090581548323149</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C66">
         <v>162</v>
@@ -2322,21 +2322,21 @@
         <v>93</v>
       </c>
       <c r="E66">
-        <v>0.2690416647275762</v>
+        <v>0.2425994100266084</v>
       </c>
       <c r="F66">
-        <v>0.4937415244625256</v>
+        <v>0.4756569408207484</v>
       </c>
       <c r="G66">
-        <v>-0.2246998597349494</v>
+        <v>-0.23305753079414</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C67">
         <v>162</v>
@@ -2345,21 +2345,21 @@
         <v>93</v>
       </c>
       <c r="E67">
-        <v>0.2487246907865033</v>
+        <v>0.2412581717356533</v>
       </c>
       <c r="F67">
-        <v>0.4577828456188182</v>
+        <v>0.456493248369959</v>
       </c>
       <c r="G67">
-        <v>-0.2090581548323149</v>
+        <v>-0.2152350766343056</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C68">
         <v>162</v>
@@ -2368,21 +2368,21 @@
         <v>93</v>
       </c>
       <c r="E68">
-        <v>0.2425994100266084</v>
+        <v>0.2697150394227307</v>
       </c>
       <c r="F68">
-        <v>0.4756569408207484</v>
+        <v>0.4935182360499853</v>
       </c>
       <c r="G68">
-        <v>-0.23305753079414</v>
+        <v>-0.2238031966272546</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C69">
         <v>162</v>
@@ -2391,21 +2391,21 @@
         <v>93</v>
       </c>
       <c r="E69">
-        <v>0.2412581717356533</v>
+        <v>0.2326628978911676</v>
       </c>
       <c r="F69">
-        <v>0.456493248369959</v>
+        <v>0.4921948610954075</v>
       </c>
       <c r="G69">
-        <v>-0.2152350766343056</v>
+        <v>-0.2595319632042399</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C70">
         <v>162</v>
@@ -2414,21 +2414,21 @@
         <v>93</v>
       </c>
       <c r="E70">
-        <v>0.2697150394227307</v>
+        <v>0.2557637934652242</v>
       </c>
       <c r="F70">
-        <v>0.4935182360499853</v>
+        <v>0.4559759161402677</v>
       </c>
       <c r="G70">
-        <v>-0.2238031966272546</v>
+        <v>-0.2002121226750436</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C71">
         <v>162</v>
@@ -2437,21 +2437,21 @@
         <v>93</v>
       </c>
       <c r="E71">
-        <v>0.2326628978911676</v>
+        <v>0.2401208441208</v>
       </c>
       <c r="F71">
-        <v>0.4921948610954075</v>
+        <v>0.4968803622107829</v>
       </c>
       <c r="G71">
-        <v>-0.2595319632042399</v>
+        <v>-0.2567595180899829</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C72">
         <v>162</v>
@@ -2460,21 +2460,21 @@
         <v>93</v>
       </c>
       <c r="E72">
-        <v>0.2557637934652242</v>
+        <v>0.2530941761151403</v>
       </c>
       <c r="F72">
-        <v>0.4559759161402677</v>
+        <v>0.4397533729705821</v>
       </c>
       <c r="G72">
-        <v>-0.2002121226750436</v>
+        <v>-0.1866591968554417</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C73">
         <v>162</v>
@@ -2483,21 +2483,21 @@
         <v>93</v>
       </c>
       <c r="E73">
-        <v>0.2401208441208</v>
+        <v>0.2651018410337679</v>
       </c>
       <c r="F73">
-        <v>0.4968803622107829</v>
+        <v>0.4279265537566853</v>
       </c>
       <c r="G73">
-        <v>-0.2567595180899829</v>
+        <v>-0.1628247127229174</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C74">
         <v>162</v>
@@ -2506,21 +2506,21 @@
         <v>93</v>
       </c>
       <c r="E74">
-        <v>0.2530941761151403</v>
+        <v>0.273814276768226</v>
       </c>
       <c r="F74">
-        <v>0.4397533729705821</v>
+        <v>0.4719602375959376</v>
       </c>
       <c r="G74">
-        <v>-0.1866591968554417</v>
+        <v>-0.1981459608277116</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C75">
         <v>162</v>
@@ -2529,81 +2529,12 @@
         <v>93</v>
       </c>
       <c r="E75">
-        <v>0.2651018410337679</v>
+        <v>0.2369427768266028</v>
       </c>
       <c r="F75">
-        <v>0.4279265537566853</v>
+        <v>0.4250895820311139</v>
       </c>
       <c r="G75">
-        <v>-0.1628247127229174</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7">
-      <c r="A76" t="s">
-        <v>79</v>
-      </c>
-      <c r="B76" t="s">
-        <v>153</v>
-      </c>
-      <c r="C76">
-        <v>162</v>
-      </c>
-      <c r="D76">
-        <v>93</v>
-      </c>
-      <c r="E76">
-        <v>0.273814276768226</v>
-      </c>
-      <c r="F76">
-        <v>0.4719602375959376</v>
-      </c>
-      <c r="G76">
-        <v>-0.1981459608277116</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
-      <c r="A77" t="s">
-        <v>38</v>
-      </c>
-      <c r="B77" t="s">
-        <v>112</v>
-      </c>
-      <c r="C77">
-        <v>162</v>
-      </c>
-      <c r="D77">
-        <v>93</v>
-      </c>
-      <c r="E77">
-        <v>0.2402002447744572</v>
-      </c>
-      <c r="F77">
-        <v>0.4510564599684409</v>
-      </c>
-      <c r="G77">
-        <v>-0.2108562151939837</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
-      <c r="A78" t="s">
-        <v>80</v>
-      </c>
-      <c r="B78" t="s">
-        <v>154</v>
-      </c>
-      <c r="C78">
-        <v>162</v>
-      </c>
-      <c r="D78">
-        <v>93</v>
-      </c>
-      <c r="E78">
-        <v>0.2369427768266028</v>
-      </c>
-      <c r="F78">
-        <v>0.4250895820311139</v>
-      </c>
-      <c r="G78">
         <v>-0.188146805204511</v>
       </c>
     </row>
